--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/afterSaleExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/afterSaleExport.xlsx
@@ -127,7 +127,7 @@
     <t>{.skuNo}</t>
   </si>
   <si>
-    <t>{.prodcutName}</t>
+    <t>{.productName}</t>
   </si>
   <si>
     <t>{.skuQty}</t>
@@ -1128,6 +1128,9 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="8" width="30.625" customWidth="1"/>
+    <col min="11" max="11" width="25.125" customWidth="1"/>
+    <col min="13" max="13" width="15.5" customWidth="1"/>
+    <col min="14" max="14" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" spans="1:22">

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/afterSaleExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/afterSaleExport.xlsx
@@ -55,7 +55,7 @@
     <t>手机号</t>
   </si>
   <si>
-    <t>客户地址</t>
+    <t>邮寄地址</t>
   </si>
   <si>
     <t>SKU</t>
@@ -67,27 +67,27 @@
     <t>数量</t>
   </si>
   <si>
-    <t>货值</t>
+    <t>单价</t>
   </si>
   <si>
     <t>维修金额</t>
   </si>
   <si>
+    <t>寄回快递单号</t>
+  </si>
+  <si>
+    <t>寄出快递单号</t>
+  </si>
+  <si>
+    <t>故障描述</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>申请日期</t>
   </si>
   <si>
-    <t>寄回快递单号</t>
-  </si>
-  <si>
-    <t>寄出快递单号</t>
-  </si>
-  <si>
-    <t>故障描述</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
     <t>审核人</t>
   </si>
   <si>
@@ -133,25 +133,25 @@
     <t>{.skuQty}</t>
   </si>
   <si>
-    <t>{.totalPrice}</t>
+    <t>{.price}</t>
   </si>
   <si>
     <t>{.totalRepairAmount}</t>
   </si>
   <si>
+    <t>{.returnTrackNo}</t>
+  </si>
+  <si>
+    <t>{.outboundTrackNo}</t>
+  </si>
+  <si>
+    <t>{.faultDesc}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
+  </si>
+  <si>
     <t>{.billDate}</t>
-  </si>
-  <si>
-    <t>{.returnTrackNo}</t>
-  </si>
-  <si>
-    <t>{.outboundTrackNo}</t>
-  </si>
-  <si>
-    <t>{.faultDesc}</t>
-  </si>
-  <si>
-    <t>{.remark}</t>
   </si>
   <si>
     <t>{.approveUserName}</t>
@@ -1131,6 +1131,7 @@
     <col min="11" max="11" width="25.125" customWidth="1"/>
     <col min="13" max="13" width="15.5" customWidth="1"/>
     <col min="14" max="14" width="13.75" customWidth="1"/>
+    <col min="21" max="21" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" spans="1:22">

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/afterSaleExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/afterSaleExport.xlsx
@@ -1128,9 +1128,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="8" width="30.625" customWidth="1"/>
-    <col min="11" max="11" width="25.125" customWidth="1"/>
+    <col min="11" max="11" width="15.25" customWidth="1"/>
     <col min="13" max="13" width="15.5" customWidth="1"/>
     <col min="14" max="14" width="13.75" customWidth="1"/>
+    <col min="19" max="19" width="20.375" customWidth="1"/>
     <col min="21" max="21" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/afterSaleExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/afterSaleExport.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>工单号</t>
   </si>
@@ -85,6 +85,12 @@
     <t>备注</t>
   </si>
   <si>
+    <t>客服备注</t>
+  </si>
+  <si>
+    <t>维修备注</t>
+  </si>
+  <si>
     <t>申请日期</t>
   </si>
   <si>
@@ -149,6 +155,12 @@
   </si>
   <si>
     <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{.csrRemark}</t>
+  </si>
+  <si>
+    <t>{.rmaRemark}</t>
   </si>
   <si>
     <t>{.billDate}</t>
@@ -1124,18 +1136,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="8" width="30.625" customWidth="1"/>
     <col min="11" max="11" width="15.25" customWidth="1"/>
     <col min="13" max="13" width="15.5" customWidth="1"/>
     <col min="14" max="14" width="13.75" customWidth="1"/>
-    <col min="19" max="19" width="20.375" customWidth="1"/>
-    <col min="21" max="21" width="8.875" customWidth="1"/>
+    <col min="18" max="18" width="12.375" customWidth="1"/>
+    <col min="19" max="19" width="13.75" customWidth="1"/>
+    <col min="20" max="20" width="12.75" customWidth="1"/>
+    <col min="21" max="21" width="15.5" customWidth="1"/>
+    <col min="23" max="23" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:22">
+    <row r="1" customFormat="1" spans="1:24">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1202,73 +1217,85 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="S2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="T2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="U2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
+      </c>
+      <c r="W2" t="s">
+        <v>46</v>
+      </c>
+      <c r="X2" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/afterSaleExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/afterSaleExport.xlsx
@@ -73,10 +73,10 @@
     <t>维修金额</t>
   </si>
   <si>
-    <t>寄回快递单号</t>
-  </si>
-  <si>
-    <t>寄出快递单号</t>
+    <t>买家寄出快递单号</t>
+  </si>
+  <si>
+    <t>商家寄出快递单号</t>
   </si>
   <si>
     <t>故障描述</t>
@@ -786,8 +786,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1143,6 +1146,8 @@
     <col min="11" max="11" width="15.25" customWidth="1"/>
     <col min="13" max="13" width="15.5" customWidth="1"/>
     <col min="14" max="14" width="13.75" customWidth="1"/>
+    <col min="15" max="15" width="15.25" customWidth="1"/>
+    <col min="16" max="16" width="15.875" customWidth="1"/>
     <col min="18" max="18" width="12.375" customWidth="1"/>
     <col min="19" max="19" width="13.75" customWidth="1"/>
     <col min="20" max="20" width="12.75" customWidth="1"/>
@@ -1150,7 +1155,7 @@
     <col min="23" max="23" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:24">
+    <row r="1" customFormat="1" ht="19" customHeight="1" spans="1:24">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1196,7 +1201,7 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="Q1" t="s">

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/afterSaleExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/afterSaleExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>工单号</t>
   </si>
@@ -37,6 +37,9 @@
     <t>订单编号</t>
   </si>
   <si>
+    <t>售后人员</t>
+  </si>
+  <si>
     <t>审核状态</t>
   </si>
   <si>
@@ -107,6 +110,9 @@
   </si>
   <si>
     <t>{.platformCode}</t>
+  </si>
+  <si>
+    <t>{.csAgentName}</t>
   </si>
   <si>
     <t>{.approveStatusName}</t>
@@ -1139,23 +1145,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="8" width="30.625" customWidth="1"/>
-    <col min="11" max="11" width="15.25" customWidth="1"/>
-    <col min="13" max="13" width="15.5" customWidth="1"/>
-    <col min="14" max="14" width="13.75" customWidth="1"/>
-    <col min="15" max="15" width="15.25" customWidth="1"/>
-    <col min="16" max="16" width="15.875" customWidth="1"/>
-    <col min="18" max="18" width="12.375" customWidth="1"/>
-    <col min="19" max="19" width="13.75" customWidth="1"/>
-    <col min="20" max="20" width="12.75" customWidth="1"/>
-    <col min="21" max="21" width="15.5" customWidth="1"/>
-    <col min="23" max="23" width="8.875" customWidth="1"/>
+    <col min="1" max="9" width="30.625" customWidth="1"/>
+    <col min="12" max="12" width="15.25" customWidth="1"/>
+    <col min="14" max="14" width="15.5" customWidth="1"/>
+    <col min="15" max="15" width="13.75" customWidth="1"/>
+    <col min="16" max="16" width="15.25" customWidth="1"/>
+    <col min="17" max="17" width="15.875" customWidth="1"/>
+    <col min="19" max="19" width="12.375" customWidth="1"/>
+    <col min="20" max="20" width="13.75" customWidth="1"/>
+    <col min="21" max="21" width="12.75" customWidth="1"/>
+    <col min="22" max="22" width="15.5" customWidth="1"/>
+    <col min="24" max="24" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="19" customHeight="1" spans="1:24">
+    <row r="1" customFormat="1" ht="19" customHeight="1" spans="1:25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1201,10 +1207,10 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="R1" t="s">
@@ -1228,79 +1234,85 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X2" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/afterSaleExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/afterSaleExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>工单号</t>
   </si>
@@ -82,6 +82,9 @@
     <t>商家寄出快递单号</t>
   </si>
   <si>
+    <t>商家寄出快递渠道</t>
+  </si>
+  <si>
     <t>故障描述</t>
   </si>
   <si>
@@ -155,6 +158,9 @@
   </si>
   <si>
     <t>{.outboundTrackNo}</t>
+  </si>
+  <si>
+    <t>{.logisticsChannelName}</t>
   </si>
   <si>
     <t>{.faultDesc}</t>
@@ -1145,7 +1151,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="9" width="30.625" customWidth="1"/>
@@ -1153,15 +1159,16 @@
     <col min="14" max="14" width="15.5" customWidth="1"/>
     <col min="15" max="15" width="13.75" customWidth="1"/>
     <col min="16" max="16" width="15.25" customWidth="1"/>
-    <col min="17" max="17" width="15.875" customWidth="1"/>
-    <col min="19" max="19" width="12.375" customWidth="1"/>
-    <col min="20" max="20" width="13.75" customWidth="1"/>
-    <col min="21" max="21" width="12.75" customWidth="1"/>
-    <col min="22" max="22" width="15.5" customWidth="1"/>
-    <col min="24" max="24" width="8.875" customWidth="1"/>
+    <col min="17" max="17" width="20.375" customWidth="1"/>
+    <col min="18" max="18" width="26" customWidth="1"/>
+    <col min="20" max="20" width="12.375" customWidth="1"/>
+    <col min="21" max="21" width="13.75" customWidth="1"/>
+    <col min="22" max="22" width="12.75" customWidth="1"/>
+    <col min="23" max="23" width="15.5" customWidth="1"/>
+    <col min="25" max="25" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="19" customHeight="1" spans="1:25">
+    <row r="1" customFormat="1" ht="19" customHeight="1" spans="1:26">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1213,7 +1220,7 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="S1" t="s">
@@ -1237,82 +1244,88 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y2" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/afterSaleExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/afterSaleExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>工单号</t>
   </si>
   <si>
-    <t>订单编号</t>
+    <t>平台名称</t>
+  </si>
+  <si>
+    <t>平台单号</t>
   </si>
   <si>
     <t>售后人员</t>
@@ -110,6 +113,9 @@
   </si>
   <si>
     <t>{.code}</t>
+  </si>
+  <si>
+    <t>{.dictPlatformName}</t>
   </si>
   <si>
     <t>{.platformCode}</t>
@@ -1151,24 +1157,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="9" width="30.625" customWidth="1"/>
-    <col min="12" max="12" width="15.25" customWidth="1"/>
-    <col min="14" max="14" width="15.5" customWidth="1"/>
-    <col min="15" max="15" width="13.75" customWidth="1"/>
-    <col min="16" max="16" width="15.25" customWidth="1"/>
-    <col min="17" max="17" width="20.375" customWidth="1"/>
-    <col min="18" max="18" width="26" customWidth="1"/>
-    <col min="20" max="20" width="12.375" customWidth="1"/>
-    <col min="21" max="21" width="13.75" customWidth="1"/>
-    <col min="22" max="22" width="12.75" customWidth="1"/>
-    <col min="23" max="23" width="15.5" customWidth="1"/>
-    <col min="25" max="25" width="8.875" customWidth="1"/>
+    <col min="1" max="10" width="30.625" customWidth="1"/>
+    <col min="13" max="13" width="15.25" customWidth="1"/>
+    <col min="15" max="15" width="15.5" customWidth="1"/>
+    <col min="16" max="16" width="13.75" customWidth="1"/>
+    <col min="17" max="17" width="15.25" customWidth="1"/>
+    <col min="18" max="18" width="20.375" customWidth="1"/>
+    <col min="19" max="19" width="26" customWidth="1"/>
+    <col min="21" max="21" width="12.375" customWidth="1"/>
+    <col min="22" max="22" width="13.75" customWidth="1"/>
+    <col min="23" max="23" width="12.75" customWidth="1"/>
+    <col min="24" max="24" width="15.5" customWidth="1"/>
+    <col min="26" max="26" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="19" customHeight="1" spans="1:26">
+    <row r="1" customFormat="1" ht="19" customHeight="1" spans="1:27">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1217,13 +1223,13 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="T1" t="s">
@@ -1247,85 +1253,91 @@
       <c r="Z1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="U2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="X2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Y2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z2" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
